--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/feb-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/feb-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>18747.45</v>
+        <v>18680.7</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1046.32</v>
+        <v>1042.59</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2225.1</v>
+        <v>2217.17</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1128.21</v>
+        <v>1124.2</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>31997.84</v>
+        <v>31883.92</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7177.11</v>
+        <v>7151.55</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5575.2</v>
+        <v>5555.35</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5314.32</v>
+        <v>5295.4</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>12540.98</v>
+        <v>12496.33</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7606.53</v>
+        <v>7579.45</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3696.39</v>
+        <v>3683.23</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8432.450000000001</v>
+        <v>8402.42</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6615.88</v>
+        <v>6592.33</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3672.07</v>
+        <v>3659</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>924.92</v>
+        <v>921.63</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7946.03</v>
+        <v>7917.74</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3574.05</v>
+        <v>3561.32</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>6023.5</v>
+        <v>6002.05</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1801.51</v>
+        <v>1788.03</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1166.87</v>
+        <v>1158.13</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2300.58</v>
+        <v>2283.37</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3429.11</v>
+        <v>3403.44</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2467.56</v>
+        <v>2449.09</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>11595.4</v>
+        <v>11508.62</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>884.03</v>
+        <v>877.41</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1367.28</v>
+        <v>1357.04</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5845.93</v>
+        <v>5802.18</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>54261.28</v>
+        <v>53855.19</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1348.73</v>
+        <v>1338.63</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1787.71</v>
+        <v>1774.33</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>16736.92</v>
+        <v>16611.66</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>28996.05</v>
+        <v>28779.05</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1695.54</v>
+        <v>1682.85</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>5107.77</v>
+        <v>5122.57</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>5766.79</v>
+        <v>5783.49</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>72882.66</v>
+        <v>73093.8</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4179.32</v>
+        <v>4191.42</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>9204.559999999999</v>
+        <v>9231.23</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2798.56</v>
+        <v>2806.67</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2785.45</v>
+        <v>2793.52</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3399.49</v>
+        <v>3409.34</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1272.83</v>
+        <v>1276.52</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2927.82</v>
+        <v>2936.3</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1749.11</v>
+        <v>1754.17</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4688.16</v>
+        <v>4701.74</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2781.69</v>
+        <v>2789.74</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>68943.71000000001</v>
+        <v>69143.44</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2178.71</v>
+        <v>2185.02</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>5521.91</v>
+        <v>5537.91</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>982.7</v>
+        <v>985.54</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2223.75</v>
+        <v>2230.19</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>877.5700000000001</v>
+        <v>880.11</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2484.65</v>
+        <v>2491.85</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>13436.65</v>
+        <v>13475.58</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>4431.05</v>
+        <v>4443.88</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3124.57</v>
+        <v>3133.63</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>16237.21</v>
+        <v>16284.25</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>31342.24</v>
+        <v>31433.04</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>22911.41</v>
+        <v>22977.79</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>6109</v>
+        <v>6126.7</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>16297.24</v>
+        <v>16344.45</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1810.01</v>
+        <v>1815.26</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1039.89</v>
+        <v>1042.91</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>6520.83</v>
+        <v>6539.72</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>35807.35</v>
+        <v>35911.08</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1574.19</v>
+        <v>1582.32</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>75484.28</v>
+        <v>75874.2</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1404.89</v>
+        <v>1412.15</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1898.71</v>
+        <v>1908.52</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1853.47</v>
+        <v>1863.05</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>5798.39</v>
+        <v>5828.34</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>8197.4</v>
+        <v>8239.74</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>19106.08</v>
+        <v>19204.77</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>9483.889999999999</v>
+        <v>9532.879999999999</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>17955.99</v>
+        <v>18048.74</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>17762.98</v>
+        <v>17854.74</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>9806.440000000001</v>
+        <v>9857.09</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1712.69</v>
+        <v>1721.54</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>45765.35</v>
+        <v>46001.75</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>942.46</v>
+        <v>938.48</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1291.56</v>
+        <v>1286.12</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>818.42</v>
+        <v>814.97</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2121.31</v>
+        <v>2112.37</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1518.02</v>
+        <v>1511.62</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>18107.34</v>
+        <v>18030.99</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1406.83</v>
+        <v>1400.9</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>12501.61</v>
+        <v>12448.9</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>11152.51</v>
+        <v>11105.49</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>14127.82</v>
+        <v>14068.25</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>8069.24</v>
+        <v>8035.22</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2996.99</v>
+        <v>2984.35</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>3901.76</v>
+        <v>3885.31</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>19333.78</v>
+        <v>19386.86</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>21375.42</v>
+        <v>21434.11</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>36832.61</v>
+        <v>36933.73</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>62773.11</v>
+        <v>62945.44</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1268.64</v>
+        <v>1272.13</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1300.55</v>
+        <v>1304.12</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>7801.3</v>
+        <v>7822.72</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2181.84</v>
+        <v>2187.83</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2613.41</v>
+        <v>2620.59</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1895.97</v>
+        <v>1901.18</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1446.59</v>
+        <v>1450.56</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1274.34</v>
+        <v>1277.83</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>12517.7</v>
+        <v>12552.06</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>4606.58</v>
+        <v>4619.23</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>7543.6</v>
+        <v>7612.21</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1399.49</v>
+        <v>1412.22</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>5792.42</v>
+        <v>5845.11</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>18657.17</v>
+        <v>18826.87</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3471.15</v>
+        <v>3502.72</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>5527.02</v>
+        <v>5577.29</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>4466.62</v>
+        <v>4507.24</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1381.84</v>
+        <v>1394.41</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>969.92</v>
+        <v>978.74</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>824.87</v>
+        <v>832.38</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2021.97</v>
+        <v>2040.36</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>12364.28</v>
+        <v>12476.75</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>823.13</v>
+        <v>830.61</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>862.33</v>
+        <v>870.17</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>3708.89</v>
+        <v>3742.63</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>5160.18</v>
+        <v>5207.12</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>4118.87</v>
+        <v>4147.55</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>4780.34</v>
+        <v>4813.62</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>6110.58</v>
+        <v>6153.12</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1198.54</v>
+        <v>1206.88</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>10172.69</v>
+        <v>10243.52</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>4577.67</v>
+        <v>4609.54</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>12740.33</v>
+        <v>12829.03</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1127.92</v>
+        <v>1135.77</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1065.41</v>
+        <v>1072.83</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>23606.18</v>
+        <v>23770.53</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1014.1</v>
+        <v>1021.16</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>20707.18</v>
+        <v>20851.34</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>8303.549999999999</v>
+        <v>8361.360000000001</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2163.9</v>
+        <v>2178.97</v>
       </c>
     </row>
     <row r="138">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>16269.92</v>
+        <v>16383.2</v>
       </c>
     </row>
     <row r="139">
@@ -8934,7 +8934,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>25722.18</v>
+        <v>25901.26</v>
       </c>
     </row>
     <row r="140">
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1984.78</v>
+        <v>1997.85</v>
       </c>
     </row>
     <row r="141">
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1296.1</v>
+        <v>1304.63</v>
       </c>
     </row>
     <row r="142">
@@ -9117,7 +9117,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>908.3099999999999</v>
+        <v>914.29</v>
       </c>
     </row>
     <row r="143">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>817.59</v>
+        <v>822.97</v>
       </c>
     </row>
     <row r="144">
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2670.4</v>
+        <v>2687.98</v>
       </c>
     </row>
     <row r="145">
@@ -9300,7 +9300,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>4693.16</v>
+        <v>4724.07</v>
       </c>
     </row>
     <row r="146">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>818.35</v>
+        <v>823.74</v>
       </c>
     </row>
     <row r="147">
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2638.55</v>
+        <v>2655.93</v>
       </c>
     </row>
     <row r="148">
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>23203.28</v>
+        <v>23356.09</v>
       </c>
     </row>
     <row r="149">
@@ -9544,7 +9544,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1059.71</v>
+        <v>1066.69</v>
       </c>
     </row>
     <row r="150">
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1083.4</v>
+        <v>1090.53</v>
       </c>
     </row>
     <row r="151">
@@ -9666,7 +9666,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>31152.43</v>
+        <v>31357.59</v>
       </c>
     </row>
     <row r="152">
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>3951.9</v>
+        <v>3977.92</v>
       </c>
     </row>
     <row r="153">
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>18936.06</v>
+        <v>19060.77</v>
       </c>
     </row>
     <row r="154">
@@ -9849,7 +9849,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>3090.59</v>
+        <v>3110.94</v>
       </c>
     </row>
     <row r="155">
@@ -9910,7 +9910,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>7573.37</v>
+        <v>7623.24</v>
       </c>
     </row>
     <row r="156">
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>4237.24</v>
+        <v>4265.15</v>
       </c>
     </row>
     <row r="157">
@@ -10032,7 +10032,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2860.36</v>
+        <v>2879.2</v>
       </c>
     </row>
     <row r="158">
@@ -10093,7 +10093,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>4092.07</v>
+        <v>4128.52</v>
       </c>
     </row>
     <row r="159">
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>1478.25</v>
+        <v>1491.42</v>
       </c>
     </row>
     <row r="160">
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1527.06</v>
+        <v>1540.67</v>
       </c>
     </row>
     <row r="161">
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>4861.91</v>
+        <v>4905.21</v>
       </c>
     </row>
     <row r="162">
@@ -10337,7 +10337,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>818.6</v>
+        <v>825.89</v>
       </c>
     </row>
     <row r="163">
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>13712.57</v>
+        <v>13834.7</v>
       </c>
     </row>
     <row r="164">
@@ -10459,7 +10459,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>3028.98</v>
+        <v>3055.96</v>
       </c>
     </row>
     <row r="165">
@@ -10520,7 +10520,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>5928.91</v>
+        <v>5981.71</v>
       </c>
     </row>
     <row r="166">
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>13118.43</v>
+        <v>13235.27</v>
       </c>
     </row>
     <row r="167">
@@ -10642,7 +10642,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1089.44</v>
+        <v>1099.14</v>
       </c>
     </row>
     <row r="168">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>5054.09</v>
+        <v>5099.1</v>
       </c>
     </row>
     <row r="169">
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>7498.98</v>
+        <v>7565.77</v>
       </c>
     </row>
     <row r="170">
@@ -10825,7 +10825,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1350.11</v>
+        <v>1362.13</v>
       </c>
     </row>
     <row r="171">
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>18756.87</v>
+        <v>18923.94</v>
       </c>
     </row>
     <row r="172">
@@ -10947,7 +10947,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>3918.62</v>
+        <v>3953.53</v>
       </c>
     </row>
     <row r="173">
@@ -11008,7 +11008,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>2275.14</v>
+        <v>2295.4</v>
       </c>
     </row>
     <row r="174">
@@ -11069,7 +11069,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>22945.76</v>
+        <v>23150.13</v>
       </c>
     </row>
     <row r="175">
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>57411.89</v>
+        <v>57923.24</v>
       </c>
     </row>
     <row r="176">
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1631.17</v>
+        <v>1645.7</v>
       </c>
     </row>
     <row r="177">
@@ -11252,7 +11252,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>3094.66</v>
+        <v>3122.22</v>
       </c>
     </row>
     <row r="178">
@@ -11313,7 +11313,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1548.23</v>
+        <v>1562.02</v>
       </c>
     </row>
     <row r="179">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1140.85</v>
+        <v>1151.01</v>
       </c>
     </row>
     <row r="180">
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>11594.25</v>
+        <v>11697.52</v>
       </c>
     </row>
     <row r="181">
@@ -11496,7 +11496,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>5787.95</v>
+        <v>5839.5</v>
       </c>
     </row>
     <row r="182">
@@ -11557,7 +11557,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1096.29</v>
+        <v>1106.06</v>
       </c>
     </row>
     <row r="183">
@@ -11618,7 +11618,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>16292.41</v>
+        <v>16264.48</v>
       </c>
     </row>
     <row r="184">
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>4727.99</v>
+        <v>4719.89</v>
       </c>
     </row>
     <row r="185">
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>4236.56</v>
+        <v>4229.3</v>
       </c>
     </row>
     <row r="186">
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2825.76</v>
+        <v>2820.92</v>
       </c>
     </row>
     <row r="187">
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1994.18</v>
+        <v>1990.77</v>
       </c>
     </row>
     <row r="188">
@@ -11923,7 +11923,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>54179.5</v>
+        <v>54086.64</v>
       </c>
     </row>
     <row r="189">
@@ -11984,7 +11984,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>21536.82</v>
+        <v>21499.91</v>
       </c>
     </row>
     <row r="190">
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1224.19</v>
+        <v>1222.09</v>
       </c>
     </row>
     <row r="191">
@@ -12106,7 +12106,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>4099.02</v>
+        <v>4092</v>
       </c>
     </row>
     <row r="192">
@@ -12167,7 +12167,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>8352.58</v>
+        <v>8338.27</v>
       </c>
     </row>
     <row r="193">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>11053.35</v>
+        <v>11034.41</v>
       </c>
     </row>
     <row r="194">
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>12423.69</v>
+        <v>12402.4</v>
       </c>
     </row>
     <row r="195">
@@ -12350,7 +12350,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>6094.81</v>
+        <v>6084.37</v>
       </c>
     </row>
     <row r="196">
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>31447.99</v>
+        <v>31394.09</v>
       </c>
     </row>
     <row r="197">
@@ -12472,7 +12472,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>17476.86</v>
+        <v>17458.83</v>
       </c>
     </row>
     <row r="198">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1153.57</v>
+        <v>1152.38</v>
       </c>
     </row>
     <row r="199">
@@ -12594,7 +12594,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>2930.77</v>
+        <v>2927.74</v>
       </c>
     </row>
     <row r="200">
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>5186.5</v>
+        <v>5181.15</v>
       </c>
     </row>
     <row r="201">
@@ -12716,7 +12716,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>3827.82</v>
+        <v>3823.87</v>
       </c>
     </row>
     <row r="202">
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>37962.81</v>
+        <v>37923.66</v>
       </c>
     </row>
     <row r="203">
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>17259.96</v>
+        <v>17242.15</v>
       </c>
     </row>
     <row r="204">
@@ -12899,7 +12899,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>6196.1</v>
+        <v>6189.71</v>
       </c>
     </row>
     <row r="205">
@@ -12960,7 +12960,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>3624.6</v>
+        <v>3620.86</v>
       </c>
     </row>
     <row r="206">
@@ -13021,7 +13021,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>2546.96</v>
+        <v>2544.34</v>
       </c>
     </row>
     <row r="207">
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1020.33</v>
+        <v>1013.02</v>
       </c>
     </row>
     <row r="208">
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2397.29</v>
+        <v>2380.12</v>
       </c>
     </row>
     <row r="209">
@@ -13204,7 +13204,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>2243.44</v>
+        <v>2227.37</v>
       </c>
     </row>
     <row r="210">
@@ -13265,7 +13265,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>5399.74</v>
+        <v>5361.06</v>
       </c>
     </row>
     <row r="211">
@@ -13326,7 +13326,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>821.36</v>
+        <v>815.47</v>
       </c>
     </row>
     <row r="212">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>10443.32</v>
+        <v>10368.5</v>
       </c>
     </row>
     <row r="213">
@@ -13448,7 +13448,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>1739.4</v>
+        <v>1726.94</v>
       </c>
     </row>
     <row r="214">
@@ -13509,7 +13509,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>2331.36</v>
+        <v>2314.66</v>
       </c>
     </row>
     <row r="215">
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>9600.01</v>
+        <v>9531.24</v>
       </c>
     </row>
     <row r="216">
@@ -13631,7 +13631,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>3344.17</v>
+        <v>3320.21</v>
       </c>
     </row>
     <row r="217">
@@ -13692,7 +13692,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1576.51</v>
+        <v>1565.21</v>
       </c>
     </row>
     <row r="218">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>15425.78</v>
+        <v>15315.27</v>
       </c>
     </row>
     <row r="219">
@@ -13814,7 +13814,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>9168.139999999999</v>
+        <v>9102.459999999999</v>
       </c>
     </row>
     <row r="220">
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>3866.44</v>
+        <v>3838.75</v>
       </c>
     </row>
     <row r="221">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1272.77</v>
+        <v>1270.9</v>
       </c>
     </row>
     <row r="222">
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>18332.75</v>
+        <v>18305.78</v>
       </c>
     </row>
     <row r="223">
@@ -14058,7 +14058,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>1465.25</v>
+        <v>1463.1</v>
       </c>
     </row>
     <row r="224">
@@ -14119,7 +14119,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>2713.07</v>
+        <v>2709.08</v>
       </c>
     </row>
     <row r="225">
@@ -14180,7 +14180,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1206.22</v>
+        <v>1204.45</v>
       </c>
     </row>
     <row r="226">
@@ -14241,7 +14241,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>11705.73</v>
+        <v>11688.5</v>
       </c>
     </row>
     <row r="227">
@@ -14302,7 +14302,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>19208.31</v>
+        <v>19180.05</v>
       </c>
     </row>
     <row r="228">
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>5585.91</v>
+        <v>5577.69</v>
       </c>
     </row>
     <row r="229">
@@ -14424,7 +14424,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>30562.16</v>
+        <v>30517.2</v>
       </c>
     </row>
     <row r="230">
@@ -14485,7 +14485,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>1393.21</v>
+        <v>1391.16</v>
       </c>
     </row>
     <row r="231">
@@ -14546,7 +14546,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>22542.87</v>
+        <v>22509.7</v>
       </c>
     </row>
     <row r="232">
@@ -14607,7 +14607,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>10120.9</v>
+        <v>10106.01</v>
       </c>
     </row>
     <row r="233">
@@ -14668,7 +14668,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>2326.1</v>
+        <v>2322.68</v>
       </c>
     </row>
     <row r="234">
@@ -14729,7 +14729,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1532.19</v>
+        <v>1529.94</v>
       </c>
     </row>
     <row r="235">
@@ -14790,7 +14790,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>812.89</v>
+        <v>811.6900000000001</v>
       </c>
     </row>
     <row r="236">
@@ -14851,7 +14851,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>16920.59</v>
+        <v>16895.7</v>
       </c>
     </row>
     <row r="237">
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>10481.31</v>
+        <v>10424.23</v>
       </c>
     </row>
     <row r="238">
@@ -14973,7 +14973,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>3599.27</v>
+        <v>3579.67</v>
       </c>
     </row>
     <row r="239">
@@ -15034,7 +15034,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>39909.24</v>
+        <v>39691.91</v>
       </c>
     </row>
     <row r="240">
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>7827.31</v>
+        <v>7784.69</v>
       </c>
     </row>
     <row r="241">
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>6513.32</v>
+        <v>6477.85</v>
       </c>
     </row>
     <row r="242">
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>9696.959999999999</v>
+        <v>9644.16</v>
       </c>
     </row>
     <row r="243">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1322.34</v>
+        <v>1315.14</v>
       </c>
     </row>
     <row r="244">
@@ -15339,7 +15339,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>3835.72</v>
+        <v>3814.83</v>
       </c>
     </row>
     <row r="245">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>993.9400000000001</v>
+        <v>988.53</v>
       </c>
     </row>
     <row r="246">
@@ -15461,7 +15461,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>4196.41</v>
+        <v>4173.55</v>
       </c>
     </row>
     <row r="247">
@@ -15522,7 +15522,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>9629.41</v>
+        <v>9576.969999999999</v>
       </c>
     </row>
     <row r="248">
@@ -15583,7 +15583,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>8149.23</v>
+        <v>8104.86</v>
       </c>
     </row>
     <row r="249">
@@ -15644,7 +15644,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1792.31</v>
+        <v>1782.55</v>
       </c>
     </row>
     <row r="250">
@@ -15705,7 +15705,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>8098.77</v>
+        <v>8054.67</v>
       </c>
     </row>
     <row r="251">
@@ -15766,7 +15766,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>30902.38</v>
+        <v>30734.1</v>
       </c>
     </row>
     <row r="252">
@@ -15827,7 +15827,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>3137.69</v>
+        <v>3120.6</v>
       </c>
     </row>
     <row r="253">
@@ -15888,7 +15888,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>77766.00999999999</v>
+        <v>77342.52</v>
       </c>
     </row>
     <row r="254">
@@ -15949,7 +15949,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>42242.52</v>
+        <v>42012.48</v>
       </c>
     </row>
     <row r="255">
@@ -16010,7 +16010,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>1855.41</v>
+        <v>1845.31</v>
       </c>
     </row>
     <row r="256">
@@ -16075,7 +16075,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>103617.74</v>
+        <v>103053.47</v>
       </c>
     </row>
     <row r="257">
@@ -16136,7 +16136,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>32993.43</v>
+        <v>32813.76</v>
       </c>
     </row>
     <row r="258">
@@ -16197,7 +16197,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>20544.76</v>
+        <v>20423.69</v>
       </c>
     </row>
     <row r="259">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>6216.98</v>
+        <v>6180.35</v>
       </c>
     </row>
     <row r="260">
@@ -16319,7 +16319,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>78715.98</v>
+        <v>78252.11</v>
       </c>
     </row>
     <row r="261">
@@ -16380,7 +16380,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>3986.83</v>
+        <v>3963.33</v>
       </c>
     </row>
     <row r="262">
@@ -16441,7 +16441,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>3365.61</v>
+        <v>3345.77</v>
       </c>
     </row>
     <row r="263">
@@ -16502,7 +16502,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>929.08</v>
+        <v>923.61</v>
       </c>
     </row>
     <row r="264">
@@ -16563,7 +16563,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>1611.02</v>
+        <v>1601.52</v>
       </c>
     </row>
     <row r="265">
@@ -16624,7 +16624,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>23987.57</v>
+        <v>23846.21</v>
       </c>
     </row>
     <row r="266">
@@ -16685,7 +16685,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1444.52</v>
+        <v>1436.01</v>
       </c>
     </row>
     <row r="267">
@@ -16746,7 +16746,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>1241.45</v>
+        <v>1234.14</v>
       </c>
     </row>
     <row r="268">
@@ -16807,7 +16807,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>7996.34</v>
+        <v>7949.22</v>
       </c>
     </row>
     <row r="269">
@@ -16868,7 +16868,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>5353.88</v>
+        <v>5322.33</v>
       </c>
     </row>
     <row r="270">
@@ -16929,7 +16929,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>9530.67</v>
+        <v>9474.51</v>
       </c>
     </row>
     <row r="271">
@@ -16990,7 +16990,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>27029.54</v>
+        <v>26865.29</v>
       </c>
     </row>
     <row r="272">
@@ -17051,7 +17051,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>825.15</v>
+        <v>820.14</v>
       </c>
     </row>
     <row r="273">
@@ -17112,7 +17112,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>1016.18</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="274">
@@ -17173,7 +17173,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1677.91</v>
+        <v>1667.71</v>
       </c>
     </row>
     <row r="275">
@@ -17234,7 +17234,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>49284.66</v>
+        <v>48985.18</v>
       </c>
     </row>
     <row r="276">
@@ -17295,7 +17295,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>3142.94</v>
+        <v>3123.84</v>
       </c>
     </row>
     <row r="277">
@@ -17356,7 +17356,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2536.87</v>
+        <v>2521.46</v>
       </c>
     </row>
     <row r="278">
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>8115.48</v>
+        <v>8066.17</v>
       </c>
     </row>
     <row r="279">
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>11251.23</v>
+        <v>11182.87</v>
       </c>
     </row>
     <row r="280">
@@ -17539,7 +17539,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>5959.53</v>
+        <v>5923.31</v>
       </c>
     </row>
     <row r="281">
@@ -17600,7 +17600,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>962.26</v>
+        <v>956.41</v>
       </c>
     </row>
     <row r="282">
@@ -17661,7 +17661,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>1182.34</v>
+        <v>1175.15</v>
       </c>
     </row>
     <row r="283">
@@ -17722,7 +17722,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>812.08</v>
+        <v>808.95</v>
       </c>
     </row>
     <row r="284">
@@ -17783,7 +17783,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>846.33</v>
+        <v>843.0700000000001</v>
       </c>
     </row>
     <row r="285">
@@ -17844,7 +17844,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>6121.55</v>
+        <v>6097.92</v>
       </c>
     </row>
     <row r="286">
@@ -17905,7 +17905,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>7759.02</v>
+        <v>7729.08</v>
       </c>
     </row>
     <row r="287">
@@ -17966,7 +17966,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>1187.07</v>
+        <v>1182.49</v>
       </c>
     </row>
     <row r="288">
@@ -18027,7 +18027,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>8031.04</v>
+        <v>8000.05</v>
       </c>
     </row>
     <row r="289">
@@ -18088,7 +18088,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>1833.62</v>
+        <v>1826.54</v>
       </c>
     </row>
     <row r="290">
@@ -18149,7 +18149,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>808.11</v>
+        <v>812.3</v>
       </c>
     </row>
     <row r="291">
@@ -18210,7 +18210,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>15152.56</v>
+        <v>15231.01</v>
       </c>
     </row>
     <row r="292">
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>14911.93</v>
+        <v>14989.13</v>
       </c>
     </row>
     <row r="293">
@@ -18332,7 +18332,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1035.22</v>
+        <v>1040.58</v>
       </c>
     </row>
     <row r="294">
@@ -18393,7 +18393,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>2751.44</v>
+        <v>2765.68</v>
       </c>
     </row>
     <row r="295">
@@ -18454,7 +18454,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>2740.69</v>
+        <v>2754.88</v>
       </c>
     </row>
     <row r="296">
@@ -18515,7 +18515,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>9209.969999999999</v>
+        <v>9257.66</v>
       </c>
     </row>
     <row r="297">
@@ -18576,7 +18576,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>1548.19</v>
+        <v>1556.2</v>
       </c>
     </row>
     <row r="298">
@@ -18637,7 +18637,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>7464.46</v>
+        <v>7503.11</v>
       </c>
     </row>
     <row r="299">
@@ -18698,7 +18698,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>991.46</v>
+        <v>996.59</v>
       </c>
     </row>
     <row r="300">
@@ -18759,7 +18759,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>2982.8</v>
+        <v>2985.67</v>
       </c>
     </row>
     <row r="301">
@@ -18820,7 +18820,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>11066.47</v>
+        <v>11077.14</v>
       </c>
     </row>
     <row r="302">
@@ -18881,7 +18881,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>1434.76</v>
+        <v>1436.14</v>
       </c>
     </row>
     <row r="303">
@@ -18942,7 +18942,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>811.52</v>
+        <v>812.3</v>
       </c>
     </row>
     <row r="304">
@@ -19003,7 +19003,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>869.91</v>
+        <v>870.75</v>
       </c>
     </row>
     <row r="305">
@@ -19064,7 +19064,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>14647.7</v>
+        <v>14661.82</v>
       </c>
     </row>
     <row r="306">
@@ -19125,7 +19125,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>3975.68</v>
+        <v>3979.51</v>
       </c>
     </row>
     <row r="307">
@@ -19186,7 +19186,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>7478.31</v>
+        <v>7485.51</v>
       </c>
     </row>
     <row r="308">
@@ -19247,7 +19247,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>6814.59</v>
+        <v>6821.16</v>
       </c>
     </row>
     <row r="309">
@@ -19308,7 +19308,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>34047.57</v>
+        <v>34080.38</v>
       </c>
     </row>
     <row r="310">
@@ -19369,7 +19369,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>2444.43</v>
+        <v>2446.79</v>
       </c>
     </row>
     <row r="311">
@@ -19430,7 +19430,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>11599.54</v>
+        <v>11610.72</v>
       </c>
     </row>
     <row r="312">
@@ -19491,7 +19491,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>2429.51</v>
+        <v>2431.85</v>
       </c>
     </row>
     <row r="313">
@@ -19552,7 +19552,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>2683.28</v>
+        <v>2685.86</v>
       </c>
     </row>
     <row r="314">
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>4439.33</v>
+        <v>4443.61</v>
       </c>
     </row>
     <row r="315">
@@ -19674,7 +19674,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>5773.16</v>
+        <v>5778.72</v>
       </c>
     </row>
     <row r="316">
@@ -19735,7 +19735,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>1401.52</v>
+        <v>1402.87</v>
       </c>
     </row>
     <row r="317">
@@ -19796,7 +19796,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>12277.63</v>
+        <v>12289.46</v>
       </c>
     </row>
     <row r="318">
@@ -19857,7 +19857,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>3838.56</v>
+        <v>3842.26</v>
       </c>
     </row>
     <row r="319">
@@ -19918,7 +19918,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>923.04</v>
+        <v>923.9299999999999</v>
       </c>
     </row>
     <row r="320">
@@ -19979,7 +19979,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>3048.67</v>
+        <v>3051.6</v>
       </c>
     </row>
     <row r="321">
@@ -20040,7 +20040,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>3788.04</v>
+        <v>3791.69</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/feb-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/feb-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12696,7 +12696,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -13367,7 +13367,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15929,7 +15929,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -17275,7 +17275,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17336,7 +17336,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17397,7 +17397,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17580,7 +17580,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17946,7 +17946,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -18739,7 +18739,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -19105,7 +19105,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19288,7 +19288,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19715,7 +19715,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/feb-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/feb-2026.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Comando de Operaciones Navales</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del Centro de Cumpli</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CCP de Rengo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmeria</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;AMP; EXPORTADORA UNINNOV EIRL</t>
+          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;amp; EXPORTADORA UNINNOV EIRL</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>Ilustre Municipalidad de Tolten</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE PUERTO WILLIAMS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SLEP IQUIQUE</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmería</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEGURIDAD INDUSTRIAL SPA </t>
+          <t xml:space="preserve">Seguridad Industrial SPA </t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>DIRECCION DE SEGURIDAD Y OPERACIONES MARITIMAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA ORLANDO ANTONIO</t>
+          <t>Comercializadora orlando antonio</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11105,7 +11105,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12813,7 +12813,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA PROINMIN SPA</t>
+          <t>Importadora y Comercializadora Proinmin SpA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DIRECCION DE INTERESES MARITIMOS Y MEDIO AMBIENTE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13362,7 +13362,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>ESCUELA DE GRUMETES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13423,7 +13423,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>Ilustre Municipalidad de Tolten</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -15192,7 +15192,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CASTRO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15253,7 +15253,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15802,7 +15802,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16046,7 +16046,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16294,7 +16294,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16599,7 +16599,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16660,7 +16660,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17463,7 +17463,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>ENERGÍA DEL FUTURO</t>
+          <t>Energía del Futuro</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17636,12 +17636,12 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -18124,7 +18124,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18439,7 +18439,7 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -18551,7 +18551,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18673,7 +18673,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -19344,7 +19344,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -19771,7 +19771,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/feb-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/feb-2026.xlsx
@@ -9403,7 +9403,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15546,7 +15550,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18928,7 +18936,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/feb-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/feb-2026.xlsx
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -15278,7 +15278,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
